--- a/study/note.xlsx
+++ b/study/note.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ERP\study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14830765-F79C-4490-8922-1C74822CA2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348C1DC3-90C0-4448-872E-C58114F2A69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
@@ -808,6 +808,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.6328125" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="14.1796875" customWidth="1"/>
     <col min="12" max="12" width="15.6328125" customWidth="1"/>
   </cols>

--- a/study/note.xlsx
+++ b/study/note.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ERP\study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348C1DC3-90C0-4448-872E-C58114F2A69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7A6E70-D140-46F6-8057-12B673937DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
-    <sheet name="Serialization" sheetId="2" r:id="rId2"/>
-    <sheet name="MVC" sheetId="3" r:id="rId3"/>
-    <sheet name="Bean" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="Serialization" sheetId="2" r:id="rId3"/>
+    <sheet name="MVC" sheetId="3" r:id="rId4"/>
+    <sheet name="Bean" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
   <si>
     <t>Chọn sản phẩm</t>
   </si>
@@ -226,6 +227,45 @@
   </si>
   <si>
     <t>DI (dependency injection)trong spring là gì?</t>
+  </si>
+  <si>
+    <t>inventory</t>
+  </si>
+  <si>
+    <t>1-n</t>
+  </si>
+  <si>
+    <t>inventory_id &lt;------</t>
+  </si>
+  <si>
+    <t>Thông tin chung</t>
+  </si>
+  <si>
+    <t>Ngày nhập</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (mặc định ngày hôm nay)</t>
+  </si>
+  <si>
+    <t>Người nhập</t>
+  </si>
+  <si>
+    <t>Nhân viên đang đăng nhập</t>
+  </si>
+  <si>
+    <t>Thông tin chi tiết</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp</t>
+  </si>
+  <si>
+    <t>Mã phiếu nhập</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm</t>
+  </si>
+  <si>
+    <t>Tổng tiền</t>
   </si>
 </sst>
 </file>
@@ -247,15 +287,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -263,16 +309,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,12 +674,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J21"/>
+  <dimension ref="A2:R44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.6328125" customWidth="1"/>
     <col min="5" max="7" width="15.54296875" customWidth="1"/>
     <col min="8" max="8" width="18.453125" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -568,11 +690,23 @@
       <c r="E2" t="s">
         <v>29</v>
       </c>
+      <c r="G2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
@@ -757,13 +891,172 @@
         <v>19</v>
       </c>
     </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="27" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="F27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="9">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="H29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="37" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="E37" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="8"/>
+      <c r="H37" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="8"/>
+      <c r="K37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="N37" t="s">
+        <v>2</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>3</v>
+      </c>
+      <c r="R37">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="E39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="8"/>
+      <c r="H39" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="8"/>
+      <c r="K39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="8"/>
+      <c r="O39">
+        <v>2</v>
+      </c>
+      <c r="R39">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="41" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="E41" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="H41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="8"/>
+      <c r="K41" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" s="8"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B44" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C31:D31"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B8C176-A2A2-4ABB-8EA8-E5458CA9C9CB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4697563-3732-4639-94E7-0A2D23D25434}">
   <dimension ref="B3:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -802,7 +1095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618F59A3-EF62-45BA-B5BC-83F73BA17DF4}">
   <dimension ref="B2:L16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -911,7 +1204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CD01FE-10D7-4013-B2C9-629536FA017A}">
   <dimension ref="C3:I9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
